--- a/Simmen_Hladik_1998/Simmen_Hladik_1998_registry_rows.xlsx
+++ b/Simmen_Hladik_1998/Simmen_Hladik_1998_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R966c99d84d0c40db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R2fa8d68a020e44c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rc609756db8a04307"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Rd24de240fb5c4774"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R605c58e900764396"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rcb97bab4395b41d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Sucrose, fructose and quinine hydrochloride thresholds</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Source tables / results to select</x:v>
+        <x:v>Table 1: Species, mean body weight and taste thresholds</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — primary source only for a demonstrated gap
@@ -350,13 +350,13 @@
         <x:v>Nicholas Saddler dissertation: Methods, Table 2 note and References (local final dissertation). Norlen 2019 Table 1/discussion; Redin Hurtado 2023 Table 1.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 2 / printed p. 130. Sucrose, fructose and quinine HCl thresholds; published sources plus unpublished results. Preserve the quinine column multiplier and per-row references. Compare with Norlen/Redin before extraction.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/0047610719/simmen_hladik_1998.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -514,7 +514,9 @@
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Table 1</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +527,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Nick: cited; direct data use not established. Planned folder: Simmen_Hladik_1998. Target: Source tables / results to select. Determine primary versus reused values per row. Keep sweet and bitter compounds separate. Full-text table selection and provenance review pending.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote correction 2026-10-25: Verified in EndNote full text — PDF p. 2 / printed p. 130. Sucrose, fructose and quinine HCl thresholds; published sources plus unpublished results. Preserve the quinine column multiplier and per-row references. Compare with Norlen/Redin before extraction. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/0047610719/simmen_hladik_1998.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — primary source only for a demonstrated gap</x:v>
@@ -562,7 +564,9 @@
       </x:c>
       <x:c r="AC2" s="3"/>
       <x:c r="AD2" s="3"/>
-      <x:c r="AE2" s="3"/>
+      <x:c r="AE2" s="3" t="str">
+        <x:v>both</x:v>
+      </x:c>
       <x:c r="AF2" s="3"/>
       <x:c r="AG2" s="3" t="str">
         <x:v>Check the Norlen 2019 and Redin Hurtado 2023 tables first. Re-extract only missing species/compounds/endpoints or protocol details; bitter/astringent endpoints may differ from compiled carbohydrate thresholds. Coverage not yet compared row by row. Use existing dataset values first, then a suitable compilation with original-source links. Extract a primary paper only for a documented missing observation/condition or ambiguity. A new folder or DOI is not evidence of new data. Shared observations count once; unresolved overlap stays on hold.</x:v>
@@ -701,7 +705,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>Blank Item number means full text is still required or the source is REFERENCE ONLY. The six EndNote PDFs identified on 2026-10-25 are linked in Source list and their source-folder notes. Smaers 2013 Table 1 is now verified. Human snapshot checks remain pending.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -985,13 +989,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1AAE82-FFAF-4441-B20D-D3072E153671}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18766230-1BD0-48E4-A352-97F0F961AD4D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89503757-AF65-4899-95DB-40C2749359E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F490AF03-21CD-49A7-B83B-4951E2D73374}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56672A79-7E2F-4120-BD17-B56B9343434F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1270939-0405-49AB-94BB-0119631BFC6F}"/>
 </file>